--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,55 +439,85 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Tipo Versamento</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Importo iniziale EUR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PAC mensile EUR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Proxy Ticker</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Proxy usato</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Proxy Nome</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Ultimo prezzo proxy</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Rendimento proxy 1D %</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>Rendimento proxy 1M %</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Rendimento proxy 3M %</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Rendimento proxy 1Y %</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Trend proxy</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Costo annuo %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Bollo una tantum EUR</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>Azione pratica</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Fonte dato</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Aggiornato UTC</t>
         </is>
@@ -516,47 +546,69 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>PAC</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>150</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>WCLD.MI</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>WisdomTree Cloud Computing UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>35.34</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10.61</v>
-      </c>
-      <c r="I2" t="n">
-        <v>28.95</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Trend positivo</t>
-        </is>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>WCLD.MI</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cloud / tecnologia / AI proxy</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>34.875</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="O2" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Positivo</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
         <v>1.8</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Non inseguire: attendere consolidamento o PAC graduale</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Non inseguire: meglio PAC/ingressi graduali</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -583,47 +635,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>PAC</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>EIMI.MI</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI EM IMI UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="J3" t="n">
-        <v>35.81</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>EIMI.MI</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Emerging markets proxy</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>47.405</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O3" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
         <v>0.3</v>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Tenere in PAC e rivalutare peso tra 3-6 mesi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Tenere monitorato come satellite; rivalutare peso tra 3-6 mesi</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -650,47 +724,69 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>VHYL.MI</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Vanguard FTSE All-World High Dividend Yield UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>81.48</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="J4" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>VHYL.MI</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>High dividend global proxy</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>81.53</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="O4" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
         <v>3.4</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Monitorare: costo elevato, serve rendimento coerente nel tempo</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R4" t="n">
+        <v>6</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Monitorare costo elevato: deve battere alternative piu' economiche</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -717,47 +813,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>SWDA.MI</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>126.32</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J5" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MSCI World / global proxy</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>126.41</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
         <v>1.39</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Mantenere monitoraggio: confrontare con benchmark/proxy</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Monitoraggio ordinario vs benchmark/proxy</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -784,47 +902,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>SWDA.MI</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>126.32</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J6" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MSCI World / global proxy</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>126.41</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O6" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
         <v>1.39</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Mantenere monitoraggio: confrontare con benchmark/proxy</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Monitoraggio ordinario vs benchmark/proxy</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -851,47 +991,69 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>SWDA.MI</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI World UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>126.32</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="J7" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SWDA.MI</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>MSCI World / growth proxy</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>126.41</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>1.39</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Mantenere monitoraggio: confrontare con benchmark/proxy</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R7" t="n">
+        <v>6</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Monitoraggio ordinario vs benchmark/proxy</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>
@@ -918,47 +1080,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Una tantum</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>EXSA.DE</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>iShares STOXX Europe 600 UCITS ETF</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>64.55</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22.12</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Laterale / neutro</t>
-        </is>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EXSA.DE</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Europa large cap proxy</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>64.59</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="O8" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Laterale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
         <v>0.3</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Tenere in PAC e rivalutare peso tra 3-6 mesi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Proxy ETF Yahoo/yfinance</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2026-09-02T13:37:02+00:00</t>
+      <c r="R8" t="n">
+        <v>6</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Tenere monitorato come satellite; rivalutare peso tra 3-6 mesi</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Yahoo/yfinance</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-02T14:16:14+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.875</v>
+        <v>34.75</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9.15</v>
+        <v>8.76</v>
       </c>
       <c r="N2" t="n">
-        <v>27.26</v>
+        <v>26.8</v>
       </c>
       <c r="O2" t="n">
-        <v>18.87</v>
+        <v>18.44</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.405</v>
+        <v>47.485</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="N3" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="O3" t="n">
-        <v>36.28</v>
+        <v>36.51</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.53</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="n">
-        <v>5.41</v>
+        <v>5.7</v>
       </c>
       <c r="O4" t="n">
-        <v>27.37</v>
+        <v>27.73</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.41</v>
+        <v>126.82</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.09</v>
+        <v>-0.77</v>
       </c>
       <c r="N5" t="n">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>21.89</v>
+        <v>22.28</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.41</v>
+        <v>126.82</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.09</v>
+        <v>-0.77</v>
       </c>
       <c r="N6" t="n">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>21.89</v>
+        <v>22.28</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.41</v>
+        <v>126.82</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.09</v>
+        <v>-0.77</v>
       </c>
       <c r="N7" t="n">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
       <c r="O7" t="n">
-        <v>21.89</v>
+        <v>22.28</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.59</v>
+        <v>64.53</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.49</v>
+        <v>-1.59</v>
       </c>
       <c r="N8" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="O8" t="n">
-        <v>22.19</v>
+        <v>22.08</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-02T14:16:14+00:00</t>
+          <t>2026-09-02T21:11:26+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.75</v>
+        <v>35.46</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.76</v>
+        <v>9.09</v>
       </c>
       <c r="N2" t="n">
-        <v>26.8</v>
+        <v>30.7</v>
       </c>
       <c r="O2" t="n">
-        <v>18.44</v>
+        <v>21.15</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.485</v>
+        <v>47.54</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>1.64</v>
       </c>
       <c r="N3" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>36.51</v>
+        <v>35.93</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.76000000000001</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7</v>
+        <v>1.39</v>
       </c>
       <c r="N4" t="n">
-        <v>5.7</v>
+        <v>6.84</v>
       </c>
       <c r="O4" t="n">
-        <v>27.73</v>
+        <v>28.59</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.82</v>
+        <v>127.84</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.77</v>
+        <v>-0.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2.82</v>
+        <v>4.21</v>
       </c>
       <c r="O5" t="n">
-        <v>22.28</v>
+        <v>22.45</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.82</v>
+        <v>127.84</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.77</v>
+        <v>-0.33</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>4.21</v>
       </c>
       <c r="O6" t="n">
-        <v>22.28</v>
+        <v>22.45</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.82</v>
+        <v>127.84</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.77</v>
+        <v>-0.33</v>
       </c>
       <c r="N7" t="n">
-        <v>2.82</v>
+        <v>4.21</v>
       </c>
       <c r="O7" t="n">
-        <v>22.28</v>
+        <v>22.45</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.53</v>
+        <v>64.98</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.59</v>
+        <v>-0.87</v>
       </c>
       <c r="N8" t="n">
-        <v>4.17</v>
+        <v>5.04</v>
       </c>
       <c r="O8" t="n">
-        <v>22.08</v>
+        <v>22.05</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-02T21:11:26+00:00</t>
+          <t>2026-09-03T21:10:46+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>35.46</v>
+        <v>34.625</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9.09</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>30.7</v>
+        <v>32.06</v>
       </c>
       <c r="O2" t="n">
-        <v>21.15</v>
+        <v>17.97</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -660,23 +660,23 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.54</v>
+        <v>48.24</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.64</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>4.64</v>
       </c>
       <c r="O3" t="n">
-        <v>35.93</v>
+        <v>38.24</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Rimbalzo breve</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>82.29000000000001</v>
+        <v>82.11</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.39</v>
+        <v>0.95</v>
       </c>
       <c r="N4" t="n">
-        <v>6.84</v>
+        <v>7.24</v>
       </c>
       <c r="O4" t="n">
-        <v>28.59</v>
+        <v>27.44</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.84</v>
+        <v>127.44</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.33</v>
+        <v>-0.51</v>
       </c>
       <c r="N5" t="n">
-        <v>4.21</v>
+        <v>5.43</v>
       </c>
       <c r="O5" t="n">
-        <v>22.45</v>
+        <v>21.07</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.84</v>
+        <v>127.44</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.33</v>
+        <v>-0.51</v>
       </c>
       <c r="N6" t="n">
-        <v>4.21</v>
+        <v>5.43</v>
       </c>
       <c r="O6" t="n">
-        <v>22.45</v>
+        <v>21.07</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.84</v>
+        <v>127.44</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.33</v>
+        <v>-0.51</v>
       </c>
       <c r="N7" t="n">
-        <v>4.21</v>
+        <v>5.43</v>
       </c>
       <c r="O7" t="n">
-        <v>22.45</v>
+        <v>21.07</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.98</v>
+        <v>65</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.87</v>
+        <v>-1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>5.04</v>
+        <v>5.63</v>
       </c>
       <c r="O8" t="n">
-        <v>22.05</v>
+        <v>21.38</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-03T21:10:46+00:00</t>
+          <t>2026-09-04T20:53:41+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,23 +571,23 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.625</v>
+        <v>34.295</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.470000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>32.06</v>
+        <v>32.16</v>
       </c>
       <c r="O2" t="n">
-        <v>17.97</v>
+        <v>13.65</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Positivo</t>
+          <t>Laterale</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -598,7 +598,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Non inseguire: meglio PAC/ingressi graduali</t>
+          <t>Tenere monitorato come satellite; rivalutare peso tra 3-6 mesi</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.24</v>
+        <v>48.38</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>4.24</v>
       </c>
       <c r="N3" t="n">
-        <v>4.64</v>
+        <v>4.21</v>
       </c>
       <c r="O3" t="n">
-        <v>38.24</v>
+        <v>36.9</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>82.11</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.95</v>
+        <v>0.33</v>
       </c>
       <c r="N4" t="n">
-        <v>7.24</v>
+        <v>6.16</v>
       </c>
       <c r="O4" t="n">
-        <v>27.44</v>
+        <v>27.87</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.44</v>
+        <v>127.41</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.51</v>
+        <v>-1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="O5" t="n">
-        <v>21.07</v>
+        <v>21.12</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.44</v>
+        <v>127.41</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.51</v>
+        <v>-1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="O6" t="n">
-        <v>21.07</v>
+        <v>21.12</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.44</v>
+        <v>127.41</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.51</v>
+        <v>-1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>5.43</v>
+        <v>5.39</v>
       </c>
       <c r="O7" t="n">
-        <v>21.07</v>
+        <v>21.12</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.07</v>
+        <v>-1.47</v>
       </c>
       <c r="N8" t="n">
-        <v>5.63</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>21.38</v>
+        <v>20.79</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-04T20:53:41+00:00</t>
+          <t>2026-09-07T11:21:41+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.295</v>
+        <v>34.085</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0.47</v>
       </c>
       <c r="N2" t="n">
-        <v>32.16</v>
+        <v>31.35</v>
       </c>
       <c r="O2" t="n">
-        <v>13.65</v>
+        <v>12.96</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.38</v>
+        <v>48.415</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="N3" t="n">
-        <v>4.21</v>
+        <v>4.29</v>
       </c>
       <c r="O3" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.90000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="N4" t="n">
-        <v>6.16</v>
+        <v>6.05</v>
       </c>
       <c r="O4" t="n">
-        <v>27.87</v>
+        <v>27.74</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.41</v>
+        <v>127.33</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="O5" t="n">
-        <v>21.12</v>
+        <v>21.05</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.41</v>
+        <v>127.33</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="O6" t="n">
-        <v>21.12</v>
+        <v>21.05</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.41</v>
+        <v>127.33</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.04</v>
+        <v>-1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5.39</v>
+        <v>5.33</v>
       </c>
       <c r="O7" t="n">
-        <v>21.12</v>
+        <v>21.05</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.93000000000001</v>
+        <v>64.97</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.47</v>
+        <v>-1.41</v>
       </c>
       <c r="N8" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
       <c r="O8" t="n">
-        <v>20.79</v>
+        <v>20.86</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-07T11:21:41+00:00</t>
+          <t>2026-09-07T17:54:27+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-07T17:54:27+00:00</t>
+          <t>2026-09-07T21:45:23+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.085</v>
+        <v>34.13</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.47</v>
+        <v>0.6</v>
       </c>
       <c r="N2" t="n">
-        <v>31.35</v>
+        <v>31.52</v>
       </c>
       <c r="O2" t="n">
-        <v>12.96</v>
+        <v>13.11</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.415</v>
+        <v>48.46</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.32</v>
+        <v>4.42</v>
       </c>
       <c r="N3" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="O3" t="n">
-        <v>37</v>
+        <v>37.13</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.81999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="N4" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="O4" t="n">
-        <v>27.74</v>
+        <v>27.62</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.33</v>
+        <v>127.34</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>-1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="O5" t="n">
-        <v>21.05</v>
+        <v>21.06</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.33</v>
+        <v>127.34</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>-1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="O6" t="n">
-        <v>21.05</v>
+        <v>21.06</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.33</v>
+        <v>127.34</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1025,10 +1025,10 @@
         <v>-1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="O7" t="n">
-        <v>21.05</v>
+        <v>21.06</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.97</v>
+        <v>64.98</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
       <c r="O8" t="n">
-        <v>20.86</v>
+        <v>20.88</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-07T21:45:23+00:00</t>
+          <t>2026-09-08T12:16:48+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>34.13</v>
+        <v>33.51</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6</v>
+        <v>-1.22</v>
       </c>
       <c r="N2" t="n">
-        <v>31.52</v>
+        <v>29.13</v>
       </c>
       <c r="O2" t="n">
-        <v>13.11</v>
+        <v>11.05</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.46</v>
+        <v>48.565</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.42</v>
+        <v>4.64</v>
       </c>
       <c r="N3" t="n">
-        <v>4.38</v>
+        <v>4.61</v>
       </c>
       <c r="O3" t="n">
-        <v>37.13</v>
+        <v>37.42</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.73999999999999</v>
+        <v>81.73</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="N4" t="n">
-        <v>5.95</v>
+        <v>5.94</v>
       </c>
       <c r="O4" t="n">
-        <v>27.62</v>
+        <v>27.6</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.34</v>
+        <v>127.17</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="N5" t="n">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="O5" t="n">
-        <v>21.06</v>
+        <v>20.9</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.34</v>
+        <v>127.17</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="N6" t="n">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="O6" t="n">
-        <v>21.06</v>
+        <v>20.9</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.34</v>
+        <v>127.17</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1</v>
+        <v>-1.23</v>
       </c>
       <c r="N7" t="n">
-        <v>5.34</v>
+        <v>5.19</v>
       </c>
       <c r="O7" t="n">
-        <v>21.06</v>
+        <v>20.9</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.98</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4</v>
+        <v>-1.47</v>
       </c>
       <c r="N8" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>20.88</v>
+        <v>20.79</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-08T12:16:48+00:00</t>
+          <t>2026-09-08T16:51:24+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-08T16:51:24+00:00</t>
+          <t>2026-09-08T21:22:46+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,23 +571,23 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.51</v>
+        <v>33.385</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.22</v>
+        <v>-2.48</v>
       </c>
       <c r="N2" t="n">
-        <v>29.13</v>
+        <v>28.31</v>
       </c>
       <c r="O2" t="n">
-        <v>11.05</v>
+        <v>10.07</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.565</v>
+        <v>48.265</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4.64</v>
+        <v>3.42</v>
       </c>
       <c r="N3" t="n">
-        <v>4.61</v>
+        <v>0.85</v>
       </c>
       <c r="O3" t="n">
-        <v>37.42</v>
+        <v>35.4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.73</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>5.94</v>
+        <v>3.76</v>
       </c>
       <c r="O4" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>127.17</v>
+        <v>126.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.23</v>
+        <v>-1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>5.19</v>
+        <v>2.91</v>
       </c>
       <c r="O5" t="n">
-        <v>20.9</v>
+        <v>20.13</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>127.17</v>
+        <v>126.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.23</v>
+        <v>-1.8</v>
       </c>
       <c r="N6" t="n">
-        <v>5.19</v>
+        <v>2.91</v>
       </c>
       <c r="O6" t="n">
-        <v>20.9</v>
+        <v>20.13</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>127.17</v>
+        <v>126.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.23</v>
+        <v>-1.8</v>
       </c>
       <c r="N7" t="n">
-        <v>5.19</v>
+        <v>2.91</v>
       </c>
       <c r="O7" t="n">
-        <v>20.9</v>
+        <v>20.13</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,23 +1105,23 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.93000000000001</v>
+        <v>64.16</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.47</v>
+        <v>-2.71</v>
       </c>
       <c r="N8" t="n">
-        <v>4.95</v>
+        <v>1.8</v>
       </c>
       <c r="O8" t="n">
-        <v>20.79</v>
+        <v>19.29</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-08T21:22:46+00:00</t>
+          <t>2026-09-09T10:34:33+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.385</v>
+        <v>33.125</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.48</v>
+        <v>-3.24</v>
       </c>
       <c r="N2" t="n">
-        <v>28.31</v>
+        <v>27.31</v>
       </c>
       <c r="O2" t="n">
-        <v>10.07</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.265</v>
+        <v>48.28</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="O3" t="n">
-        <v>35.4</v>
+        <v>35.45</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.23999999999999</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>26.3</v>
+        <v>25.99</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -838,23 +838,23 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.4</v>
+        <v>126.03</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="O5" t="n">
-        <v>20.13</v>
+        <v>19.78</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -927,23 +927,23 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.4</v>
+        <v>126.03</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="O6" t="n">
-        <v>20.13</v>
+        <v>19.78</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.4</v>
+        <v>126.03</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8</v>
+        <v>-2.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="O7" t="n">
-        <v>20.13</v>
+        <v>19.78</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.16</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.71</v>
+        <v>-2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>19.29</v>
+        <v>19.01</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-09T10:34:33+00:00</t>
+          <t>2026-09-09T17:10:30+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-09T17:10:30+00:00</t>
+          <t>2026-09-09T19:16:34+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-09T19:16:34+00:00</t>
+          <t>2026-09-09T21:44:04+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.125</v>
+        <v>32.94</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.24</v>
+        <v>-2.12</v>
       </c>
       <c r="N2" t="n">
-        <v>27.31</v>
+        <v>24.16</v>
       </c>
       <c r="O2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -660,23 +660,23 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>48.28</v>
+        <v>47.865</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>1.38</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>-2.57</v>
       </c>
       <c r="O3" t="n">
-        <v>35.45</v>
+        <v>33</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rimbalzo breve</t>
+          <t>Laterale</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.04000000000001</v>
+        <v>81.05</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>3.37</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99</v>
+        <v>25.83</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.03</v>
+        <v>125.94</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.09</v>
+        <v>-2.22</v>
       </c>
       <c r="N5" t="n">
-        <v>2.61</v>
+        <v>1.35</v>
       </c>
       <c r="O5" t="n">
-        <v>19.78</v>
+        <v>19.05</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.03</v>
+        <v>125.94</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.09</v>
+        <v>-2.22</v>
       </c>
       <c r="N6" t="n">
-        <v>2.61</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
-        <v>19.78</v>
+        <v>19.05</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.03</v>
+        <v>125.94</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.09</v>
+        <v>-2.22</v>
       </c>
       <c r="N7" t="n">
-        <v>2.61</v>
+        <v>1.35</v>
       </c>
       <c r="O7" t="n">
-        <v>19.78</v>
+        <v>19.05</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>64.01000000000001</v>
+        <v>63.78</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.94</v>
+        <v>-3.23</v>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>19.01</v>
+        <v>18.63</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-09T21:44:04+00:00</t>
+          <t>2026-09-10T12:15:32+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,23 +571,23 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>32.94</v>
+        <v>33.09</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.12</v>
+        <v>-1.68</v>
       </c>
       <c r="N2" t="n">
-        <v>24.16</v>
+        <v>24.73</v>
       </c>
       <c r="O2" t="n">
-        <v>9.75</v>
+        <v>10.24</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pressione breve</t>
+          <t>Laterale</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.865</v>
+        <v>47.36</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.38</v>
+        <v>0.31</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.57</v>
+        <v>-3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>33</v>
+        <v>31.59</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.05</v>
+        <v>80.67</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.99</v>
+        <v>-1.45</v>
       </c>
       <c r="N4" t="n">
-        <v>3.37</v>
+        <v>2.89</v>
       </c>
       <c r="O4" t="n">
-        <v>25.83</v>
+        <v>25.24</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>125.94</v>
+        <v>125.25</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.22</v>
+        <v>-2.76</v>
       </c>
       <c r="N5" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
-        <v>19.05</v>
+        <v>18.39</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>125.94</v>
+        <v>125.25</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.22</v>
+        <v>-2.76</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>19.05</v>
+        <v>18.39</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>125.94</v>
+        <v>125.25</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.22</v>
+        <v>-2.76</v>
       </c>
       <c r="N7" t="n">
-        <v>1.35</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>19.05</v>
+        <v>18.39</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>63.78</v>
+        <v>63.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.23</v>
+        <v>-3.66</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>18.63</v>
+        <v>18.11</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10T12:15:32+00:00</t>
+          <t>2026-09-10T14:30:21+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.09</v>
+        <v>33.175</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.68</v>
+        <v>-1.43</v>
       </c>
       <c r="N2" t="n">
-        <v>24.73</v>
+        <v>25.05</v>
       </c>
       <c r="O2" t="n">
-        <v>10.24</v>
+        <v>10.53</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.36</v>
+        <v>47.515</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.6</v>
+        <v>-3.29</v>
       </c>
       <c r="O3" t="n">
-        <v>31.59</v>
+        <v>32.02</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>80.67</v>
+        <v>80.64</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.45</v>
+        <v>-1.49</v>
       </c>
       <c r="N4" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="O4" t="n">
-        <v>25.24</v>
+        <v>25.2</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>125.25</v>
+        <v>125.42</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.76</v>
+        <v>-2.62</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="O5" t="n">
-        <v>18.39</v>
+        <v>18.56</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>125.25</v>
+        <v>125.42</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.76</v>
+        <v>-2.62</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="O6" t="n">
-        <v>18.39</v>
+        <v>18.56</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>125.25</v>
+        <v>125.42</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.76</v>
+        <v>-2.62</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="O7" t="n">
-        <v>18.39</v>
+        <v>18.56</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>63.5</v>
+        <v>63.49</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.66</v>
+        <v>-3.67</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="O8" t="n">
-        <v>18.11</v>
+        <v>18.09</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10T14:30:21+00:00</t>
+          <t>2026-09-10T17:00:15+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10T17:00:15+00:00</t>
+          <t>2026-09-10T19:07:48+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10T19:07:48+00:00</t>
+          <t>2026-09-10T21:40:18+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,23 +571,23 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.175</v>
+        <v>33.085</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.43</v>
+        <v>-2.39</v>
       </c>
       <c r="N2" t="n">
-        <v>25.05</v>
+        <v>27.91</v>
       </c>
       <c r="O2" t="n">
-        <v>10.53</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Laterale</t>
+          <t>Pressione breve</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.515</v>
+        <v>47.88</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.64</v>
+        <v>0.92</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.29</v>
+        <v>-1.43</v>
       </c>
       <c r="O3" t="n">
-        <v>32.02</v>
+        <v>32.06</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>80.64</v>
+        <v>81.2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.49</v>
+        <v>-0.9</v>
       </c>
       <c r="N4" t="n">
-        <v>2.85</v>
+        <v>3.52</v>
       </c>
       <c r="O4" t="n">
-        <v>25.2</v>
+        <v>24.97</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>125.42</v>
+        <v>126.26</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.62</v>
+        <v>-2.41</v>
       </c>
       <c r="N5" t="n">
-        <v>0.93</v>
+        <v>1.73</v>
       </c>
       <c r="O5" t="n">
-        <v>18.56</v>
+        <v>18.59</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>125.42</v>
+        <v>126.26</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.62</v>
+        <v>-2.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0.93</v>
+        <v>1.73</v>
       </c>
       <c r="O6" t="n">
-        <v>18.56</v>
+        <v>18.59</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>125.42</v>
+        <v>126.26</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.62</v>
+        <v>-2.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0.93</v>
+        <v>1.73</v>
       </c>
       <c r="O7" t="n">
-        <v>18.56</v>
+        <v>18.59</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>63.49</v>
+        <v>63.88</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.67</v>
+        <v>-3.11</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>18.09</v>
+        <v>18.11</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10T21:40:18+00:00</t>
+          <t>2026-09-11T12:14:04+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.085</v>
+        <v>33.015</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.39</v>
+        <v>-2.6</v>
       </c>
       <c r="N2" t="n">
-        <v>27.91</v>
+        <v>27.64</v>
       </c>
       <c r="O2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.88</v>
+        <v>47.84</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.43</v>
+        <v>-1.51</v>
       </c>
       <c r="O3" t="n">
-        <v>32.06</v>
+        <v>31.95</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.2</v>
+        <v>81.33</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9</v>
+        <v>-0.74</v>
       </c>
       <c r="N4" t="n">
-        <v>3.52</v>
+        <v>3.69</v>
       </c>
       <c r="O4" t="n">
-        <v>24.97</v>
+        <v>25.17</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.26</v>
+        <v>126.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.41</v>
+        <v>-2.23</v>
       </c>
       <c r="N5" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O5" t="n">
-        <v>18.59</v>
+        <v>18.81</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.26</v>
+        <v>126.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.41</v>
+        <v>-2.23</v>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O6" t="n">
-        <v>18.59</v>
+        <v>18.81</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.26</v>
+        <v>126.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.41</v>
+        <v>-2.23</v>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="O7" t="n">
-        <v>18.59</v>
+        <v>18.81</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>63.88</v>
+        <v>63.81</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.11</v>
+        <v>-3.22</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O8" t="n">
-        <v>18.11</v>
+        <v>17.98</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-11T12:14:04+00:00</t>
+          <t>2026-09-11T14:29:28+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>33.015</v>
+        <v>32.8</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.6</v>
+        <v>-3.23</v>
       </c>
       <c r="N2" t="n">
-        <v>27.64</v>
+        <v>26.81</v>
       </c>
       <c r="O2" t="n">
-        <v>9.470000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>47.84</v>
+        <v>48.02</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.51</v>
+        <v>-1.14</v>
       </c>
       <c r="O3" t="n">
-        <v>31.95</v>
+        <v>32.45</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -749,19 +749,19 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>81.33</v>
+        <v>81.27</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.74</v>
+        <v>-0.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3.69</v>
+        <v>3.61</v>
       </c>
       <c r="O4" t="n">
-        <v>25.17</v>
+        <v>25.08</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>126.5</v>
+        <v>126.64</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.23</v>
+        <v>-2.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
-        <v>18.81</v>
+        <v>18.94</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>126.5</v>
+        <v>126.64</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.23</v>
+        <v>-2.12</v>
       </c>
       <c r="N6" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O6" t="n">
-        <v>18.81</v>
+        <v>18.94</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>126.5</v>
+        <v>126.64</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.23</v>
+        <v>-2.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="O7" t="n">
-        <v>18.81</v>
+        <v>18.94</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>63.81</v>
+        <v>63.86</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.22</v>
+        <v>-3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="O8" t="n">
-        <v>17.98</v>
+        <v>18.07</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-11T14:29:28+00:00</t>
+          <t>2026-09-11T17:02:05+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-11T17:02:05+00:00</t>
+          <t>2026-09-11T19:09:59+00:00</t>
         </is>
       </c>
     </row>

--- a/AlphaForge_Fund_Performance.xlsx
+++ b/AlphaForge_Fund_Performance.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-11T19:09:59+00:00</t>
+          <t>2026-09-11T21:45:18+00:00</t>
         </is>
       </c>
     </row>
